--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-practitionerrole.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-practitionerrole.xlsx
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>PRD (as one example)</t>
@@ -313,16 +313,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -448,7 +448,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
